--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "MZML", "RAW"</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>RAW</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1750,7 +1750,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1760,30 +1760,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1826,14 +1826,10 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1841,30 +1837,34 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>host_organism</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Binomial name of organism with full genus name</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>"Mus musculus"</t>
+          <t>"Homo sapiens", "Mus musculus"</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1874,50 +1874,83 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Mus musculus</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>host_organism</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>"Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mus musculus</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
           <t>reported_gender</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
         <is>
           <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>"Female", "Male", "Not Reported"</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G49"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1928,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AV1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1978,6 +2011,7 @@
     <col width="24" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2193,32 +2227,37 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="14">
+  <dataValidations count="15">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2252,14 +2291,17 @@
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$L$2:$L$3</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$2</formula1>
+      <formula1>'Lists'!$M$2:$M$3</formula1>
     </dataValidation>
     <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$N$2:$N$4</formula1>
+      <formula1>'Lists'!$N$2:$N$2</formula1>
+    </dataValidation>
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$O$2:$O$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2272,7 +2314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2333,15 +2375,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>FFPE</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>reported_gender</t>
         </is>
@@ -2405,15 +2452,20 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Female</t>
         </is>
@@ -2472,10 +2524,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2512,7 +2569,7 @@
           <t>SHA256</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Not Reported</t>
         </is>
@@ -2831,14 +2888,14 @@
     <row r="25">
       <c r="E25" t="inlineStr">
         <is>
-          <t>mzML</t>
+          <t>MZML</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="E26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>RAW</t>
         </is>
       </c>
     </row>

--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -1731,7 +1731,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Number of fractions generated for sample; leave blank or use 1 if not fractionated</t>
+          <t>Number of fractions generated for sample. Required when fractionation_approach is HpH; leave blank if not fractionated</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1740,11 +1740,7 @@
           <t>integer</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="F43" s="2" t="inlineStr"/>
       <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">

--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
+          <t>Host organism binomial name when the sequenced sample is a xenograft. Required when composition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1906,11 +1906,7 @@
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">

--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -1334,7 +1334,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
+          <t>Full hash value of the file</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>

--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$20</formula1>
+      <formula1>'Lists'!$C$2:$C$21</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -2850,6 +2850,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Extracellular Vesicles</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>

--- a/excel_templates/immunopeptidomics_manifest_template.xlsx
+++ b/excel_templates/immunopeptidomics_manifest_template.xlsx
@@ -772,7 +772,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line", "Extracellular Vesicles"</t>
+          <t>"Bone Marrow", "Buffy Coat", "Derived Cell Line", "Not Available", "Not Reported", "Patient Derived Xenograft", "Xenograft", "Patient Derived Organoid", "Peripheral Blood Mononuclear Cells", "Peripheral Whole Blood", "Saliva", "Solid Tissue", "Umbilical Cord Blood", "Patient-Derived T Cells", "Modified T Cells", "Patient-Derived Primary Cells", "iPSC-Derived Organoid", "Cerebrospinal Fluid", "Embryonic Stem Cell Derived Cell Line"</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2257,7 +2257,7 @@
       <formula1>'Lists'!$B$2:$B$14</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$C$2:$C$21</formula1>
+      <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$8</formula1>
@@ -2850,11 +2850,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Extracellular Vesicles</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>
